--- a/data/trans_dic/P25D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,98</t>
+          <t>0,14; 1,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,61</t>
+          <t>0,06; 0,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,02</t>
+          <t>0,18; 1,12</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,48</t>
+          <t>0,21; 1,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,87</t>
+          <t>0,43; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,32</t>
+          <t>0,4; 1,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,45</t>
+          <t>0,47; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,65</t>
+          <t>0,24; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,93</t>
+          <t>0,48; 1,96</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,11</t>
+          <t>1,03; 3,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,04</t>
+          <t>0,28; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,8</t>
+          <t>0,74; 1,76</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,66</t>
+          <t>0,68; 1,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,97</t>
+          <t>0,42; 0,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,16</t>
+          <t>0,62; 1,15</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>868; 12549</t>
+          <t>867; 12186</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>377; 4114</t>
+          <t>376; 4237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1981; 13363</t>
+          <t>2379; 14603</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2191; 17601</t>
+          <t>2479; 17234</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3926; 17928</t>
+          <t>4119; 18384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8352; 28475</t>
+          <t>8675; 28159</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2946; 24323</t>
+          <t>3335; 24449</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2372; 15431</t>
+          <t>2196; 15584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8184; 31623</t>
+          <t>7885; 32035</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9428; 28560</t>
+          <t>9437; 28554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3409; 11341</t>
+          <t>3032; 11180</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15341; 36184</t>
+          <t>14783; 35312</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23831; 57128</t>
+          <t>23553; 57918</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15475; 35432</t>
+          <t>15300; 36286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44527; 82700</t>
+          <t>44134; 81536</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,92</t>
+          <t>0,15; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,63</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,12</t>
+          <t>0,15; 1,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,44</t>
+          <t>0,3; 1,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,92</t>
+          <t>0,41; 1,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,31</t>
+          <t>0,49; 1,36</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,47</t>
+          <t>0,46; 2,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,67</t>
+          <t>0,34; 1,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,96</t>
+          <t>0,58; 2,01</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,1</t>
+          <t>1,21; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,03</t>
+          <t>0,34; 1,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,76</t>
+          <t>0,88; 2,12</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,68</t>
+          <t>0,81; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,99</t>
+          <t>0,48; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,15</t>
+          <t>0,7; 1,27</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6120</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>867; 12186</t>
+          <t>1054; 13034</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>376; 4237</t>
+          <t>0; 4237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2379; 14603</t>
+          <t>2099; 14977</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>17366</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2479; 17234</t>
+          <t>3115; 17227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4119; 18384</t>
+          <t>4430; 18921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8675; 28159</t>
+          <t>10349; 28754</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>17441</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3335; 24449</t>
+          <t>3671; 23165</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2196; 15584</t>
+          <t>2728; 15729</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7885; 32035</t>
+          <t>9397; 32525</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>27622</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9437; 28554</t>
+          <t>11889; 35456</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3032; 11180</t>
+          <t>3815; 13025</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14783; 35312</t>
+          <t>18393; 44445</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23553; 57918</t>
+          <t>28507; 62490</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15300; 36286</t>
+          <t>17746; 39041</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44134; 81536</t>
+          <t>50758; 92172</t>
         </is>
       </c>
     </row>
